--- a/products-storage/00-free-uderzhaniya-do-podpisi/02-reestr-uderzhaniy-po-obektu.xlsx
+++ b/products-storage/00-free-uderzhaniya-do-podpisi/02-reestr-uderzhaniy-po-obektu.xlsx
@@ -816,7 +816,10 @@
           <t>ИТОГО удержано:</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr"/>
+      <c r="E15" s="2">
+        <f>SUM(E3:E14)</f>
+        <v/>
+      </c>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr"/>
@@ -827,7 +830,10 @@
           <t>ИТОГО возвращено:</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr"/>
+      <c r="L15" s="2">
+        <f>SUM(L3:L14)</f>
+        <v/>
+      </c>
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr"/>
     </row>
@@ -848,7 +854,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2. Суммы и даты вводятся руками. Формул в файле нет намеренно: итог, посчитанный формулой по неполному реестру, выглядит достоверно и таковым не является. Сверяйте итог с бухгалтерией.</t>
+          <t>2. Суммы и даты вводятся руками, итоговые строки считаются формулой по диапазону строк 3-14. Итог по неполному реестру достоверным не становится: он верен ровно настолько, насколько полон реестр. Сверяйте с бухгалтерией. Строку «ПРИМЕР» удалите — в диапазон итога она не входит.</t>
         </is>
       </c>
     </row>
